--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4288" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4287" uniqueCount="316">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:17:44+00:00</t>
+    <t>2026-03-19T09:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -436,6 +436,9 @@
     <t>motivationLocale</t>
   </si>
   <si>
+    <t>Champ libre permettant de renseigner une motivation locale</t>
+  </si>
+  <si>
     <t>Extension.extension:decision.extension:motivationLocale.id</t>
   </si>
   <si>
@@ -446,505 +449,505 @@
   </si>
   <si>
     <t>Extension.extension:decision.extension:motivationLocale.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:commentaire</t>
+  </si>
+  <si>
+    <t>commentaire</t>
+  </si>
+  <si>
+    <t>Commentaire de la décision</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:commentaire.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:commentaire.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:commentaire.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:commentaire.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation</t>
+  </si>
+  <si>
+    <t>droitPrestation</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture</t>
+  </si>
+  <si>
+    <t>dateOuverture</t>
+  </si>
+  <si>
+    <t>Date d'ouverture du droit</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance</t>
+  </si>
+  <si>
+    <t>dateEcheance</t>
+  </si>
+  <si>
+    <t>Date d'échéance du droit</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG</t>
+  </si>
+  <si>
+    <t>existencePAG</t>
+  </si>
+  <si>
+    <t>Existence d'un PAG</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:creton</t>
+  </si>
+  <si>
+    <t>creton</t>
+  </si>
+  <si>
+    <t>Indicateur creton</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:taux</t>
+  </si>
+  <si>
+    <t>taux</t>
+  </si>
+  <si>
+    <t>Taux</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire</t>
+  </si>
+  <si>
+    <t>Commentaire du droit de prestation</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation</t>
+  </si>
+  <si>
+    <t>detailPrestation</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil</t>
+  </si>
+  <si>
+    <t>temporaliteAccueil</t>
+  </si>
+  <si>
+    <t>Temporalité d'accueil</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J30-TemporaliteAccueil-ROR/FHIR/JDV-J30-TemporaliteAccueil-ROR</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel</t>
+  </si>
+  <si>
+    <t>accueilSequentiel</t>
+  </si>
+  <si>
+    <t>Accueil séquentiel</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation</t>
+  </si>
+  <si>
+    <t>formation</t>
+  </si>
+  <si>
+    <t>Formation</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue</t>
+  </si>
+  <si>
+    <t>montantAttribue</t>
+  </si>
+  <si>
+    <t>Montant attribué</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence</t>
+  </si>
+  <si>
+    <t>frequence</t>
+  </si>
+  <si>
+    <t>Fréquence</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil</t>
+  </si>
+  <si>
+    <t>structureAccueil</t>
+  </si>
+  <si>
+    <t>Structure d'accueil</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge</t>
+  </si>
+  <si>
+    <t>priseCharge</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge</t>
+  </si>
+  <si>
+    <t>modePriseCharge</t>
+  </si>
+  <si>
+    <t>Mode de prise en charge</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J264-ModeEtCentreDePriseEnCharge-MDPH/FHIR/JDV-J264-ModeEtCentreDePriseEnCharge-MDPH</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification</t>
+  </si>
+  <si>
+    <t>quantification</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge</t>
+  </si>
+  <si>
+    <t>valeurPriseCharge</t>
+  </si>
+  <si>
+    <t>Valeur de la prise en charge</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension.extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge</t>
+  </si>
+  <si>
+    <t>unitePriseCharge</t>
+  </si>
+  <si>
+    <t>Unité de la prise en charge</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge</t>
+  </si>
+  <si>
+    <t>frequencePriseCharge</t>
+  </si>
+  <si>
+    <t>Fréquence de la prise en charge</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J37-UcumUniteTemps/FHIR/JDV-J37-UcumUniteTemps</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.value[x]</t>
   </si>
   <si>
     <t>base64Binary
 booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:commentaire</t>
-  </si>
-  <si>
-    <t>commentaire</t>
-  </si>
-  <si>
-    <t>Commentaire de la décision</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:commentaire.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:commentaire.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:commentaire.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:commentaire.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation</t>
-  </si>
-  <si>
-    <t>droitPrestation</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture</t>
-  </si>
-  <si>
-    <t>dateOuverture</t>
-  </si>
-  <si>
-    <t>Date d'ouverture du droit</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.url</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateOuverture.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance</t>
-  </si>
-  <si>
-    <t>dateEcheance</t>
-  </si>
-  <si>
-    <t>Date d'échéance du droit</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:dateEcheance.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG</t>
-  </si>
-  <si>
-    <t>existencePAG</t>
-  </si>
-  <si>
-    <t>Existence d'un PAG</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:existencePAG.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:creton</t>
-  </si>
-  <si>
-    <t>creton</t>
-  </si>
-  <si>
-    <t>Indicateur creton</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:creton.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:taux</t>
-  </si>
-  <si>
-    <t>taux</t>
-  </si>
-  <si>
-    <t>Taux</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:taux.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire</t>
-  </si>
-  <si>
-    <t>Commentaire du droit de prestation</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation</t>
-  </si>
-  <si>
-    <t>detailPrestation</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil</t>
-  </si>
-  <si>
-    <t>temporaliteAccueil</t>
-  </si>
-  <si>
-    <t>Temporalité d'accueil</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.url</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J30-TemporaliteAccueil-ROR/FHIR/JDV-J30-TemporaliteAccueil-ROR</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel</t>
-  </si>
-  <si>
-    <t>accueilSequentiel</t>
-  </si>
-  <si>
-    <t>Accueil séquentiel</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:accueilSequentiel.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation</t>
-  </si>
-  <si>
-    <t>formation</t>
-  </si>
-  <si>
-    <t>Formation</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:formation.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue</t>
-  </si>
-  <si>
-    <t>montantAttribue</t>
-  </si>
-  <si>
-    <t>Montant attribué</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:montantAttribue.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Money
-</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence</t>
-  </si>
-  <si>
-    <t>frequence</t>
-  </si>
-  <si>
-    <t>Fréquence</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil</t>
-  </si>
-  <si>
-    <t>structureAccueil</t>
-  </si>
-  <si>
-    <t>Structure d'accueil</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:structureAccueil.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
-</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge</t>
-  </si>
-  <si>
-    <t>priseCharge</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge</t>
-  </si>
-  <si>
-    <t>modePriseCharge</t>
-  </si>
-  <si>
-    <t>Mode de prise en charge</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.url</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:modePriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J264-ModeEtCentreDePriseEnCharge-MDPH/FHIR/JDV-J264-ModeEtCentreDePriseEnCharge-MDPH</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification</t>
-  </si>
-  <si>
-    <t>quantification</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge</t>
-  </si>
-  <si>
-    <t>valeurPriseCharge</t>
-  </si>
-  <si>
-    <t>Valeur de la prise en charge</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.url</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:valeurPriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension.extension.extension.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge</t>
-  </si>
-  <si>
-    <t>unitePriseCharge</t>
-  </si>
-  <si>
-    <t>Unité de la prise en charge</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:unitePriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge</t>
-  </si>
-  <si>
-    <t>frequencePriseCharge</t>
-  </si>
-  <si>
-    <t>Fréquence de la prise en charge</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.extension:frequencePriseCharge.value[x]</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J37-UcumUniteTemps/FHIR/JDV-J37-UcumUniteTemps</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.extension:quantification.value[x]</t>
   </si>
   <si>
     <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:priseCharge.url</t>
@@ -3131,7 +3134,7 @@
         <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>91</v>
@@ -3205,7 +3208,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>110</v>
@@ -3308,21 +3311,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>76</v>
@@ -3337,14 +3340,12 @@
         <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3408,12 +3409,12 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>114</v>
@@ -3518,7 +3519,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>122</v>
@@ -3544,7 +3545,7 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>124</v>
@@ -13817,7 +13818,7 @@
         <v>76</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>124</v>
@@ -13894,7 +13895,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>213</v>
@@ -13999,7 +14000,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>215</v>
@@ -14025,7 +14026,7 @@
         <v>76</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>124</v>
@@ -14102,7 +14103,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>162</v>
@@ -14207,7 +14208,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>164</v>
@@ -14233,7 +14234,7 @@
         <v>76</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>124</v>
@@ -14310,7 +14311,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>114</v>
@@ -14415,7 +14416,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>122</v>
@@ -14441,7 +14442,7 @@
         <v>76</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>124</v>
@@ -14518,10 +14519,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14623,10 +14624,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14649,7 +14650,7 @@
         <v>76</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>124</v>
@@ -14857,7 +14858,7 @@
         <v>76</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>141</v>
+        <v>305</v>
       </c>
       <c r="L131" t="s" s="2">
         <v>124</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T15:24:46+00:00</t>
+    <t>2026-06-09T07:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T07:55:39+00:00</t>
+    <t>2026-06-09T09:58:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T09:58:53+00:00</t>
+    <t>2026-06-10T14:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T14:13:27+00:00</t>
+    <t>2026-06-12T15:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5413" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5735" uniqueCount="388">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:13:13+00:00</t>
+    <t>2026-06-15T13:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -680,6 +680,30 @@
 </t>
   </si>
   <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:motifFinPAG</t>
+  </si>
+  <si>
+    <t>motifFinPAG</t>
+  </si>
+  <si>
+    <t>Motif de fin du PAG</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:motifFinPAG.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:motifFinPAG.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:motifFinPAG.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:motifFinPAG.value[x]</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j403-motif-fin-pag-ms</t>
+  </si>
+  <si>
     <t>Extension.extension:decision.extension:droitPrestation.extension:creton</t>
   </si>
   <si>
@@ -726,6 +750,30 @@
 </t>
   </si>
   <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:typeCompensation</t>
+  </si>
+  <si>
+    <t>typeCompensation</t>
+  </si>
+  <si>
+    <t>Type de compensation</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:typeCompensation.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:typeCompensation.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:typeCompensation.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:decision.extension:droitPrestation.extension:typeCompensation.value[x]</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j394-type-demande-compensation-ms</t>
+  </si>
+  <si>
     <t>Extension.extension:decision.extension:droitPrestation.extension:commentaire</t>
   </si>
   <si>
@@ -754,9 +802,6 @@
   </si>
   <si>
     <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:temporaliteAccueil</t>
@@ -892,7 +937,7 @@
     <t>frequence</t>
   </si>
   <si>
-    <t>Fréquence</t>
+    <t>Fréquence de versement</t>
   </si>
   <si>
     <t>Extension.extension:decision.extension:droitPrestation.extension:detailPrestation.extension:frequence.id</t>
@@ -1458,7 +1503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK166"/>
+  <dimension ref="A1:AK176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="137.41796875" customWidth="true" bestFit="true"/>
@@ -9205,7 +9250,7 @@
         <v>76</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>120</v>
@@ -9238,13 +9283,11 @@
         <v>76</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -9282,13 +9325,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>108</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>76</v>
@@ -9313,7 +9356,7 @@
         <v>90</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>91</v>
@@ -9387,7 +9430,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>172</v>
@@ -9490,7 +9533,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>174</v>
@@ -9593,7 +9636,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>176</v>
@@ -9636,7 +9679,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>76</v>
@@ -9698,7 +9741,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>178</v>
@@ -9724,7 +9767,7 @@
         <v>76</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>120</v>
@@ -9807,7 +9850,7 @@
         <v>108</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>76</v>
@@ -9832,7 +9875,7 @@
         <v>90</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>91</v>
@@ -9906,7 +9949,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>172</v>
@@ -10009,7 +10052,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>174</v>
@@ -10112,7 +10155,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>176</v>
@@ -10155,7 +10198,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>76</v>
@@ -10217,7 +10260,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>178</v>
@@ -10243,7 +10286,7 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>120</v>
@@ -10320,20 +10363,20 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>108</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>83</v>
@@ -10351,7 +10394,7 @@
         <v>90</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>30</v>
+        <v>243</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>91</v>
@@ -10425,7 +10468,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>172</v>
@@ -10528,7 +10571,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>174</v>
@@ -10539,10 +10582,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>76</v>
@@ -10631,20 +10674,18 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>83</v>
@@ -10659,22 +10700,24 @@
         <v>76</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>246</v>
+        <v>112</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>76</v>
@@ -10716,22 +10759,22 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>76</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90">
@@ -10739,7 +10782,7 @@
         <v>247</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10762,13 +10805,13 @@
         <v>76</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10795,13 +10838,11 @@
         <v>76</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>76</v>
@@ -10819,7 +10860,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -10831,10 +10872,10 @@
         <v>76</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91">
@@ -10842,9 +10883,11 @@
         <v>249</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>76</v>
       </c>
@@ -10853,7 +10896,7 @@
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>76</v>
@@ -10868,7 +10911,7 @@
         <v>90</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>91</v>
@@ -10910,16 +10953,16 @@
         <v>76</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>95</v>
@@ -10945,7 +10988,7 @@
         <v>251</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10953,7 +10996,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>83</v>
@@ -10968,24 +11011,22 @@
         <v>76</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>245</v>
+        <v>76</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>76</v>
@@ -11027,10 +11068,10 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>83</v>
@@ -11042,15 +11083,15 @@
         <v>76</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11061,7 +11102,7 @@
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>76</v>
@@ -11073,13 +11114,13 @@
         <v>76</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11106,62 +11147,62 @@
         <v>76</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>255</v>
+        <v>76</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>83</v>
@@ -11176,22 +11217,24 @@
         <v>76</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>76</v>
@@ -11233,30 +11276,30 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>76</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11282,10 +11325,10 @@
         <v>84</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11336,7 +11379,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -11348,29 +11391,31 @@
         <v>76</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>76</v>
@@ -11427,16 +11472,16 @@
         <v>76</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>95</v>
@@ -11459,10 +11504,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11470,7 +11515,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>83</v>
@@ -11485,24 +11530,22 @@
         <v>76</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>257</v>
+        <v>76</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>76</v>
@@ -11544,10 +11587,10 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>83</v>
@@ -11559,15 +11602,15 @@
         <v>76</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11575,10 +11618,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>76</v>
@@ -11590,13 +11633,13 @@
         <v>76</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11623,55 +11666,57 @@
         <v>76</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>76</v>
@@ -11696,7 +11741,7 @@
         <v>90</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>91</v>
@@ -11770,10 +11815,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11873,10 +11918,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11976,10 +12021,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12019,7 +12064,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>76</v>
@@ -12081,10 +12126,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12107,7 +12152,7 @@
         <v>76</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>120</v>
@@ -12140,13 +12185,11 @@
         <v>76</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>76</v>
+        <v>270</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>76</v>
@@ -12292,7 +12335,7 @@
         <v>274</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12395,7 +12438,7 @@
         <v>275</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12498,7 +12541,7 @@
         <v>276</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12603,7 +12646,7 @@
         <v>277</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12626,7 +12669,7 @@
         <v>76</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>120</v>
@@ -12659,13 +12702,11 @@
         <v>76</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>76</v>
+        <v>278</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>76</v>
@@ -12703,13 +12744,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>76</v>
@@ -12734,7 +12775,7 @@
         <v>90</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>91</v>
@@ -12808,10 +12849,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12911,10 +12952,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13014,10 +13055,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13057,7 +13098,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>76</v>
@@ -13119,10 +13160,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13145,7 +13186,7 @@
         <v>76</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>285</v>
+        <v>217</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>120</v>
@@ -13330,7 +13371,7 @@
         <v>289</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13433,7 +13474,7 @@
         <v>290</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13536,7 +13577,7 @@
         <v>291</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13641,7 +13682,7 @@
         <v>292</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13664,7 +13705,7 @@
         <v>76</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>120</v>
@@ -13754,7 +13795,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>83</v>
@@ -13849,7 +13890,7 @@
         <v>296</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13952,7 +13993,7 @@
         <v>297</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14055,7 +14096,7 @@
         <v>298</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14160,7 +14201,7 @@
         <v>299</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14183,7 +14224,7 @@
         <v>76</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>119</v>
+        <v>300</v>
       </c>
       <c r="L123" t="s" s="2">
         <v>120</v>
@@ -14216,11 +14257,13 @@
         <v>76</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y123" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z123" t="s" s="2">
-        <v>300</v>
+        <v>76</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>76</v>
@@ -14271,10 +14314,10 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>76</v>
@@ -14366,7 +14409,7 @@
         <v>304</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14469,7 +14512,7 @@
         <v>305</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14572,7 +14615,7 @@
         <v>306</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14677,7 +14720,7 @@
         <v>307</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14700,7 +14743,7 @@
         <v>76</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>308</v>
+        <v>240</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>120</v>
@@ -14777,23 +14820,23 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>76</v>
@@ -14808,7 +14851,7 @@
         <v>90</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>30</v>
+        <v>310</v>
       </c>
       <c r="M129" t="s" s="2">
         <v>91</v>
@@ -14885,7 +14928,7 @@
         <v>311</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14988,18 +15031,18 @@
         <v>312</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>313</v>
+        <v>76</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>76</v>
@@ -15014,14 +15057,12 @@
         <v>90</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>314</v>
+        <v>30</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -15085,25 +15126,23 @@
         <v>81</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>83</v>
@@ -15118,22 +15157,24 @@
         <v>76</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>319</v>
+        <v>112</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>76</v>
+        <v>309</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>76</v>
@@ -15175,30 +15216,30 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>76</v>
+        <v>116</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15221,13 +15262,13 @@
         <v>76</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15254,13 +15295,11 @@
         <v>76</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>76</v>
+        <v>315</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>76</v>
@@ -15278,7 +15317,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -15290,20 +15329,22 @@
         <v>76</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C134" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D134" t="s" s="2">
         <v>76</v>
       </c>
@@ -15312,7 +15353,7 @@
         <v>77</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>76</v>
@@ -15327,7 +15368,7 @@
         <v>90</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>30</v>
+        <v>318</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>91</v>
@@ -15369,16 +15410,16 @@
         <v>76</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
         <v>95</v>
@@ -15401,10 +15442,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>325</v>
+        <v>263</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15412,7 +15453,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>83</v>
@@ -15427,24 +15468,22 @@
         <v>76</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q135" s="2"/>
       <c r="R135" t="s" s="2">
-        <v>318</v>
+        <v>76</v>
       </c>
       <c r="S135" t="s" s="2">
         <v>76</v>
@@ -15486,10 +15525,10 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>83</v>
@@ -15501,15 +15540,15 @@
         <v>76</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>327</v>
+        <v>265</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15520,7 +15559,7 @@
         <v>77</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>76</v>
@@ -15532,13 +15571,13 @@
         <v>76</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15565,62 +15604,62 @@
         <v>76</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y136" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z136" t="s" s="2">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>83</v>
@@ -15635,22 +15674,24 @@
         <v>76</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>76</v>
@@ -15692,30 +15733,30 @@
         <v>76</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>76</v>
+        <v>116</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15738,13 +15779,13 @@
         <v>76</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -15795,7 +15836,7 @@
         <v>76</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>77</v>
@@ -15807,22 +15848,24 @@
         <v>76</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="D139" t="s" s="2">
-        <v>313</v>
+        <v>76</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -15844,14 +15887,12 @@
         <v>90</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>314</v>
+        <v>30</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>76</v>
@@ -15888,16 +15929,16 @@
         <v>76</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AF139" t="s" s="2">
         <v>95</v>
@@ -15915,19 +15956,17 @@
         <v>81</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
         <v>76</v>
       </c>
@@ -15948,13 +15987,13 @@
         <v>76</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>335</v>
+        <v>85</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16005,41 +16044,41 @@
         <v>76</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>337</v>
+        <v>265</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>76</v>
+        <v>328</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>76</v>
@@ -16051,15 +16090,17 @@
         <v>76</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>76</v>
@@ -16096,31 +16137,31 @@
         <v>76</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>88</v>
@@ -16128,12 +16169,14 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D142" t="s" s="2">
         <v>76</v>
       </c>
@@ -16142,7 +16185,7 @@
         <v>77</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>76</v>
@@ -16157,7 +16200,7 @@
         <v>90</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>30</v>
+        <v>334</v>
       </c>
       <c r="M142" t="s" s="2">
         <v>91</v>
@@ -16199,16 +16242,16 @@
         <v>76</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
         <v>95</v>
@@ -16231,10 +16274,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16242,7 +16285,7 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>83</v>
@@ -16257,24 +16300,22 @@
         <v>76</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q143" s="2"/>
       <c r="R143" t="s" s="2">
-        <v>334</v>
+        <v>76</v>
       </c>
       <c r="S143" t="s" s="2">
         <v>76</v>
@@ -16316,10 +16357,10 @@
         <v>76</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>83</v>
@@ -16331,15 +16372,15 @@
         <v>76</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16350,7 +16391,7 @@
         <v>77</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>76</v>
@@ -16362,13 +16403,13 @@
         <v>76</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>344</v>
+        <v>90</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16407,52 +16448,50 @@
         <v>76</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>83</v>
@@ -16467,22 +16506,24 @@
         <v>76</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>347</v>
+        <v>112</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>76</v>
+        <v>333</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>76</v>
@@ -16524,30 +16565,30 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>76</v>
+        <v>116</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16570,13 +16611,13 @@
         <v>76</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -16603,13 +16644,11 @@
         <v>76</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>76</v>
+        <v>343</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>76</v>
@@ -16627,7 +16666,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -16639,20 +16678,22 @@
         <v>76</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C147" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="C147" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="D147" t="s" s="2">
         <v>76</v>
       </c>
@@ -16661,7 +16702,7 @@
         <v>77</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>76</v>
@@ -16718,16 +16759,16 @@
         <v>76</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
         <v>95</v>
@@ -16750,10 +16791,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16761,7 +16802,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>83</v>
@@ -16776,24 +16817,22 @@
         <v>76</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
-        <v>346</v>
+        <v>76</v>
       </c>
       <c r="S148" t="s" s="2">
         <v>76</v>
@@ -16835,10 +16874,10 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>83</v>
@@ -16850,26 +16889,26 @@
         <v>76</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>76</v>
+        <v>328</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>76</v>
@@ -16881,15 +16920,17 @@
         <v>76</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>120</v>
+        <v>329</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>76</v>
@@ -16926,45 +16967,45 @@
         <v>76</v>
       </c>
       <c r="AB149" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC149" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD149" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE149" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>76</v>
@@ -16989,7 +17030,7 @@
         <v>90</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="M150" t="s" s="2">
         <v>91</v>
@@ -17063,10 +17104,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17166,10 +17207,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17269,10 +17310,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17312,7 +17353,7 @@
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>76</v>
@@ -17374,10 +17415,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B154" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17400,7 +17441,7 @@
         <v>76</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>119</v>
+        <v>359</v>
       </c>
       <c r="L154" t="s" s="2">
         <v>120</v>
@@ -17433,11 +17474,13 @@
         <v>76</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="Y154" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z154" t="s" s="2">
-        <v>359</v>
+        <v>76</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>76</v>
@@ -17478,15 +17521,17 @@
         <v>360</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C155" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="C155" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>83</v>
@@ -17501,24 +17546,22 @@
         <v>76</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>112</v>
+        <v>362</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>330</v>
+        <v>76</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>76</v>
@@ -17560,30 +17603,30 @@
         <v>76</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17594,7 +17637,7 @@
         <v>77</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>76</v>
@@ -17606,13 +17649,13 @@
         <v>76</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>362</v>
+        <v>84</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -17663,7 +17706,7 @@
         <v>76</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>77</v>
@@ -17675,18 +17718,18 @@
         <v>76</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>252</v>
+        <v>354</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17694,10 +17737,10 @@
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>76</v>
@@ -17709,24 +17752,22 @@
         <v>76</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
-        <v>310</v>
+        <v>76</v>
       </c>
       <c r="S157" t="s" s="2">
         <v>76</v>
@@ -17756,42 +17797,42 @@
         <v>76</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>254</v>
+        <v>356</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17799,10 +17840,10 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>76</v>
@@ -17814,22 +17855,24 @@
         <v>76</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>362</v>
+        <v>111</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="N158" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q158" s="2"/>
       <c r="R158" t="s" s="2">
-        <v>76</v>
+        <v>361</v>
       </c>
       <c r="S158" t="s" s="2">
         <v>76</v>
@@ -17871,10 +17914,10 @@
         <v>76</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>83</v>
@@ -17883,7 +17926,7 @@
         <v>76</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>116</v>
@@ -17891,10 +17934,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>176</v>
+        <v>358</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17902,7 +17945,7 @@
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G159" t="s" s="2">
         <v>83</v>
@@ -17917,24 +17960,22 @@
         <v>76</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="S159" t="s" s="2">
         <v>76</v>
@@ -17976,10 +18017,10 @@
         <v>76</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>83</v>
@@ -17988,7 +18029,7 @@
         <v>76</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>116</v>
@@ -17996,12 +18037,14 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C160" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="D160" t="s" s="2">
         <v>76</v>
       </c>
@@ -18010,7 +18053,7 @@
         <v>77</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>76</v>
@@ -18022,13 +18065,13 @@
         <v>76</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>362</v>
+        <v>90</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>120</v>
+        <v>369</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -18079,30 +18122,30 @@
         <v>76</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>110</v>
+        <v>352</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18110,7 +18153,7 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>83</v>
@@ -18125,24 +18168,22 @@
         <v>76</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>76</v>
@@ -18184,10 +18225,10 @@
         <v>76</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>83</v>
@@ -18199,15 +18240,15 @@
         <v>76</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>116</v>
+        <v>88</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>118</v>
+        <v>354</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18230,13 +18271,13 @@
         <v>76</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>362</v>
+        <v>90</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -18275,42 +18316,42 @@
         <v>76</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18350,7 +18391,7 @@
       </c>
       <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
-        <v>97</v>
+        <v>368</v>
       </c>
       <c r="S163" t="s" s="2">
         <v>76</v>
@@ -18412,10 +18453,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18426,7 +18467,7 @@
         <v>77</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>76</v>
@@ -18438,7 +18479,7 @@
         <v>76</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>362</v>
+        <v>119</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>120</v>
@@ -18471,13 +18512,11 @@
         <v>76</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>76</v>
@@ -18515,10 +18554,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>115</v>
+        <v>340</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18558,7 +18597,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>3</v>
+        <v>345</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>76</v>
@@ -18620,10 +18659,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>124</v>
+        <v>376</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>124</v>
+        <v>342</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18646,7 +18685,7 @@
         <v>76</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>120</v>
@@ -18718,6 +18757,1046 @@
         <v>125</v>
       </c>
       <c r="AK166" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O167" s="2"/>
+      <c r="P167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O169" s="2"/>
+      <c r="P169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
+      <c r="P170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O171" s="2"/>
+      <c r="P171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N172" s="2"/>
+      <c r="O172" s="2"/>
+      <c r="P172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O173" s="2"/>
+      <c r="P173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N174" s="2"/>
+      <c r="O174" s="2"/>
+      <c r="P174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK176" t="s" s="2">
         <v>116</v>
       </c>
     </row>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T13:25:13+00:00</t>
+    <t>2026-06-16T07:36:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:36:31+00:00</t>
+    <t>2026-06-16T07:55:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:55:16+00:00</t>
+    <t>2026-06-16T08:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:15:37+00:00</t>
+    <t>2026-06-17T09:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:17:48+00:00</t>
+    <t>2026-06-17T09:36:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:36:47+00:00</t>
+    <t>2026-06-19T10:27:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T10:27:30+00:00</t>
+    <t>2026-06-22T09:32:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5735" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5735" uniqueCount="390">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:32:11+00:00</t>
+    <t>2026-06-24T08:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -315,6 +315,11 @@
     <t>decision</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.code='9999')
+ implies ((extension.where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
+  </si>
+  <si>
     <t>Extension.extension:decision.id</t>
   </si>
   <si>
@@ -518,6 +523,11 @@
   </si>
   <si>
     <t>droitPrestation</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
+ '6' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
   </si>
   <si>
     <t>Extension.extension:decision.extension:droitPrestation.id</t>
@@ -2065,7 +2075,7 @@
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2073,10 +2083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2176,10 +2186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2279,13 +2289,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="B8" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="C8" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>76</v>
@@ -2310,7 +2320,7 @@
         <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M8" t="s" s="2">
         <v>91</v>
@@ -2384,10 +2394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2487,10 +2497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2590,10 +2600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2616,16 +2626,16 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2633,7 +2643,7 @@
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>76</v>
@@ -2675,7 +2685,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
@@ -2690,15 +2700,15 @@
         <v>76</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2721,13 +2731,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2754,11 +2764,11 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2776,7 +2786,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2788,21 +2798,21 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>76</v>
@@ -2827,7 +2837,7 @@
         <v>90</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>91</v>
@@ -2901,10 +2911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3004,10 +3014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3107,10 +3117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3133,16 +3143,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3150,7 +3160,7 @@
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>76</v>
@@ -3192,7 +3202,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -3207,15 +3217,15 @@
         <v>76</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3238,13 +3248,13 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3295,7 +3305,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3307,21 +3317,21 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>76</v>
@@ -3346,7 +3356,7 @@
         <v>90</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>91</v>
@@ -3420,10 +3430,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3523,10 +3533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3626,10 +3636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3652,16 +3662,16 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3669,7 +3679,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>76</v>
@@ -3711,7 +3721,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -3726,15 +3736,15 @@
         <v>76</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3757,13 +3767,13 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3814,7 +3824,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3826,21 +3836,21 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>76</v>
@@ -3865,7 +3875,7 @@
         <v>90</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M23" t="s" s="2">
         <v>91</v>
@@ -3939,10 +3949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4042,10 +4052,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4145,10 +4155,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4171,16 +4181,16 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4188,7 +4198,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>76</v>
@@ -4230,7 +4240,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -4245,15 +4255,15 @@
         <v>76</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4276,13 +4286,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4309,11 +4319,11 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4331,7 +4341,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4343,21 +4353,21 @@
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>76</v>
@@ -4382,7 +4392,7 @@
         <v>90</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M28" t="s" s="2">
         <v>91</v>
@@ -4456,10 +4466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4559,10 +4569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4662,10 +4672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4688,16 +4698,16 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4705,7 +4715,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>76</v>
@@ -4747,7 +4757,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -4762,15 +4772,15 @@
         <v>76</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4796,10 +4806,10 @@
         <v>84</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4850,7 +4860,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4862,21 +4872,21 @@
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>76</v>
@@ -4901,7 +4911,7 @@
         <v>90</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M33" t="s" s="2">
         <v>91</v>
@@ -4975,10 +4985,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5078,10 +5088,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5181,10 +5191,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5207,16 +5217,16 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5224,7 +5234,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>76</v>
@@ -5266,7 +5276,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -5281,15 +5291,15 @@
         <v>76</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5315,10 +5325,10 @@
         <v>84</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5369,7 +5379,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5381,21 +5391,21 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>76</v>
@@ -5486,7 +5496,7 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>76</v>
@@ -5494,10 +5504,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5597,10 +5607,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5608,7 +5618,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>78</v>
@@ -5700,13 +5710,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>76</v>
@@ -5731,7 +5741,7 @@
         <v>90</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>91</v>
@@ -5805,10 +5815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5908,10 +5918,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6011,10 +6021,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6037,16 +6047,16 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6054,7 +6064,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>76</v>
@@ -6096,7 +6106,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -6111,15 +6121,15 @@
         <v>76</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6142,13 +6152,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6175,11 +6185,11 @@
         <v>76</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>76</v>
@@ -6197,7 +6207,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6209,21 +6219,21 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>76</v>
@@ -6248,7 +6258,7 @@
         <v>90</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>91</v>
@@ -6322,10 +6332,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6425,10 +6435,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6528,10 +6538,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6554,16 +6564,16 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6571,7 +6581,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>76</v>
@@ -6613,7 +6623,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -6628,15 +6638,15 @@
         <v>76</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6659,13 +6669,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6692,11 +6702,11 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>76</v>
@@ -6714,7 +6724,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -6726,21 +6736,21 @@
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>76</v>
@@ -6765,7 +6775,7 @@
         <v>90</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M51" t="s" s="2">
         <v>91</v>
@@ -6839,10 +6849,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6942,10 +6952,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7045,10 +7055,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7071,16 +7081,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7088,7 +7098,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>76</v>
@@ -7130,7 +7140,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -7145,15 +7155,15 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7176,13 +7186,13 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7209,11 +7219,11 @@
         <v>76</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>76</v>
@@ -7231,7 +7241,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7243,21 +7253,21 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>76</v>
@@ -7282,7 +7292,7 @@
         <v>90</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>91</v>
@@ -7356,10 +7366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7459,10 +7469,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7562,10 +7572,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7588,16 +7598,16 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7605,7 +7615,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>76</v>
@@ -7647,7 +7657,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -7662,15 +7672,15 @@
         <v>76</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7693,13 +7703,13 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7750,7 +7760,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -7762,21 +7772,21 @@
         <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>76</v>
@@ -7801,7 +7811,7 @@
         <v>90</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M61" t="s" s="2">
         <v>91</v>
@@ -7875,10 +7885,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7978,10 +7988,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8081,10 +8091,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8107,16 +8117,16 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8124,7 +8134,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>76</v>
@@ -8166,7 +8176,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -8181,15 +8191,15 @@
         <v>76</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8212,13 +8222,13 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8269,7 +8279,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8281,21 +8291,21 @@
         <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>76</v>
@@ -8320,7 +8330,7 @@
         <v>90</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>91</v>
@@ -8394,10 +8404,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8497,10 +8507,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8600,10 +8610,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8626,16 +8636,16 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8643,7 +8653,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>76</v>
@@ -8685,7 +8695,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -8700,15 +8710,15 @@
         <v>76</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8731,13 +8741,13 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8788,7 +8798,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -8800,21 +8810,21 @@
         <v>76</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>76</v>
@@ -8839,7 +8849,7 @@
         <v>90</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>91</v>
@@ -8913,10 +8923,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9016,10 +9026,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9119,10 +9129,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9145,16 +9155,16 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9162,7 +9172,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>76</v>
@@ -9204,7 +9214,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -9219,15 +9229,15 @@
         <v>76</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9250,13 +9260,13 @@
         <v>76</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9283,11 +9293,11 @@
         <v>76</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>76</v>
@@ -9305,7 +9315,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -9317,21 +9327,21 @@
         <v>76</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>76</v>
@@ -9356,7 +9366,7 @@
         <v>90</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>91</v>
@@ -9430,10 +9440,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9533,10 +9543,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9636,10 +9646,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9662,16 +9672,16 @@
         <v>76</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9679,7 +9689,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>76</v>
@@ -9721,7 +9731,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -9736,15 +9746,15 @@
         <v>76</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9767,13 +9777,13 @@
         <v>76</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9824,7 +9834,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -9836,21 +9846,21 @@
         <v>76</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>76</v>
@@ -9875,7 +9885,7 @@
         <v>90</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>91</v>
@@ -9949,10 +9959,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10052,10 +10062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10155,10 +10165,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10181,16 +10191,16 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10198,7 +10208,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>76</v>
@@ -10240,7 +10250,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -10255,15 +10265,15 @@
         <v>76</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10286,13 +10296,13 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10343,7 +10353,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -10355,21 +10365,21 @@
         <v>76</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>76</v>
@@ -10394,7 +10404,7 @@
         <v>90</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>91</v>
@@ -10468,10 +10478,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10571,10 +10581,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10674,10 +10684,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10700,16 +10710,16 @@
         <v>76</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10717,7 +10727,7 @@
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>76</v>
@@ -10759,7 +10769,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -10774,15 +10784,15 @@
         <v>76</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10805,13 +10815,13 @@
         <v>76</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10838,11 +10848,11 @@
         <v>76</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>76</v>
@@ -10860,7 +10870,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -10872,21 +10882,21 @@
         <v>76</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>76</v>
@@ -10911,7 +10921,7 @@
         <v>90</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M91" t="s" s="2">
         <v>91</v>
@@ -10985,10 +10995,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11088,10 +11098,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11191,10 +11201,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11217,16 +11227,16 @@
         <v>76</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11234,7 +11244,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>76</v>
@@ -11276,7 +11286,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -11291,15 +11301,15 @@
         <v>76</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11325,10 +11335,10 @@
         <v>84</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11379,7 +11389,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -11391,21 +11401,21 @@
         <v>76</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>76</v>
@@ -11504,10 +11514,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11607,10 +11617,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11710,13 +11720,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>76</v>
@@ -11741,7 +11751,7 @@
         <v>90</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>91</v>
@@ -11815,10 +11825,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11918,10 +11928,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12021,10 +12031,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12047,16 +12057,16 @@
         <v>76</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12064,7 +12074,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>76</v>
@@ -12106,7 +12116,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -12121,15 +12131,15 @@
         <v>76</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12152,13 +12162,13 @@
         <v>76</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12185,11 +12195,11 @@
         <v>76</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>76</v>
@@ -12207,7 +12217,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -12219,21 +12229,21 @@
         <v>76</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
@@ -12258,7 +12268,7 @@
         <v>90</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M104" t="s" s="2">
         <v>91</v>
@@ -12332,10 +12342,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12435,10 +12445,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12538,10 +12548,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12564,16 +12574,16 @@
         <v>76</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12581,7 +12591,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>76</v>
@@ -12623,7 +12633,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -12638,15 +12648,15 @@
         <v>76</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12669,13 +12679,13 @@
         <v>76</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12702,11 +12712,11 @@
         <v>76</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>76</v>
@@ -12724,7 +12734,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -12736,21 +12746,21 @@
         <v>76</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>76</v>
@@ -12775,7 +12785,7 @@
         <v>90</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>91</v>
@@ -12849,10 +12859,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12952,10 +12962,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13055,10 +13065,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13081,16 +13091,16 @@
         <v>76</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -13098,7 +13108,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>76</v>
@@ -13140,7 +13150,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -13155,15 +13165,15 @@
         <v>76</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13186,13 +13196,13 @@
         <v>76</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13243,7 +13253,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -13255,21 +13265,21 @@
         <v>76</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>76</v>
@@ -13294,7 +13304,7 @@
         <v>90</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>91</v>
@@ -13368,10 +13378,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13471,10 +13481,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13574,10 +13584,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13600,16 +13610,16 @@
         <v>76</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -13617,7 +13627,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>76</v>
@@ -13659,7 +13669,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>83</v>
@@ -13674,15 +13684,15 @@
         <v>76</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13708,10 +13718,10 @@
         <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13762,7 +13772,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -13774,21 +13784,21 @@
         <v>76</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>76</v>
@@ -13813,7 +13823,7 @@
         <v>90</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>91</v>
@@ -13887,10 +13897,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13990,10 +14000,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14093,10 +14103,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14119,16 +14129,16 @@
         <v>76</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14136,7 +14146,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>76</v>
@@ -14178,7 +14188,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -14193,15 +14203,15 @@
         <v>76</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14224,13 +14234,13 @@
         <v>76</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14281,7 +14291,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -14293,21 +14303,21 @@
         <v>76</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>76</v>
@@ -14332,7 +14342,7 @@
         <v>90</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M124" t="s" s="2">
         <v>91</v>
@@ -14406,10 +14416,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14509,10 +14519,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14612,10 +14622,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14638,16 +14648,16 @@
         <v>76</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -14655,7 +14665,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>76</v>
@@ -14697,7 +14707,7 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -14712,15 +14722,15 @@
         <v>76</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14743,13 +14753,13 @@
         <v>76</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14800,7 +14810,7 @@
         <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -14812,21 +14822,21 @@
         <v>76</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>76</v>
@@ -14851,7 +14861,7 @@
         <v>90</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M129" t="s" s="2">
         <v>91</v>
@@ -14925,10 +14935,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15028,10 +15038,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15131,10 +15141,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15157,16 +15167,16 @@
         <v>76</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -15174,7 +15184,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>76</v>
@@ -15216,7 +15226,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>83</v>
@@ -15231,15 +15241,15 @@
         <v>76</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15262,13 +15272,13 @@
         <v>76</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15295,11 +15305,11 @@
         <v>76</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>76</v>
@@ -15317,7 +15327,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>77</v>
@@ -15329,21 +15339,21 @@
         <v>76</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>76</v>
@@ -15368,7 +15378,7 @@
         <v>90</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>91</v>
@@ -15442,10 +15452,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15545,10 +15555,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15648,10 +15658,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15674,16 +15684,16 @@
         <v>76</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -15691,7 +15701,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>76</v>
@@ -15733,7 +15743,7 @@
         <v>76</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>83</v>
@@ -15748,15 +15758,15 @@
         <v>76</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15779,13 +15789,13 @@
         <v>76</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -15836,7 +15846,7 @@
         <v>76</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>77</v>
@@ -15848,21 +15858,21 @@
         <v>76</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>76</v>
@@ -15961,10 +15971,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16064,14 +16074,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -16093,13 +16103,13 @@
         <v>90</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -16169,13 +16179,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>76</v>
@@ -16200,7 +16210,7 @@
         <v>90</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M142" t="s" s="2">
         <v>91</v>
@@ -16274,10 +16284,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16377,10 +16387,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16480,10 +16490,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16506,16 +16516,16 @@
         <v>76</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -16523,7 +16533,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>76</v>
@@ -16565,7 +16575,7 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>83</v>
@@ -16580,15 +16590,15 @@
         <v>76</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16611,13 +16621,13 @@
         <v>76</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -16644,11 +16654,11 @@
         <v>76</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>76</v>
@@ -16666,7 +16676,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>77</v>
@@ -16678,21 +16688,21 @@
         <v>76</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>76</v>
@@ -16791,10 +16801,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16894,14 +16904,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -16923,13 +16933,13 @@
         <v>90</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -16999,13 +17009,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>76</v>
@@ -17030,7 +17040,7 @@
         <v>90</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M150" t="s" s="2">
         <v>91</v>
@@ -17104,10 +17114,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17207,10 +17217,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17310,10 +17320,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17336,16 +17346,16 @@
         <v>76</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -17353,7 +17363,7 @@
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>76</v>
@@ -17395,7 +17405,7 @@
         <v>76</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>83</v>
@@ -17410,15 +17420,15 @@
         <v>76</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17441,13 +17451,13 @@
         <v>76</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17498,7 +17508,7 @@
         <v>76</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>77</v>
@@ -17510,21 +17520,21 @@
         <v>76</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>76</v>
@@ -17549,7 +17559,7 @@
         <v>90</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M155" t="s" s="2">
         <v>91</v>
@@ -17623,10 +17633,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17726,10 +17736,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17829,10 +17839,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17855,16 +17865,16 @@
         <v>76</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -17872,7 +17882,7 @@
       </c>
       <c r="Q158" s="2"/>
       <c r="R158" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="S158" t="s" s="2">
         <v>76</v>
@@ -17914,7 +17924,7 @@
         <v>76</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>83</v>
@@ -17929,15 +17939,15 @@
         <v>76</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17960,13 +17970,13 @@
         <v>76</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -18017,7 +18027,7 @@
         <v>76</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>77</v>
@@ -18029,21 +18039,21 @@
         <v>76</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D160" t="s" s="2">
         <v>76</v>
@@ -18068,7 +18078,7 @@
         <v>90</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M160" t="s" s="2">
         <v>91</v>
@@ -18142,10 +18152,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18245,10 +18255,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18348,10 +18358,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18374,16 +18384,16 @@
         <v>76</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -18391,7 +18401,7 @@
       </c>
       <c r="Q163" s="2"/>
       <c r="R163" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="S163" t="s" s="2">
         <v>76</v>
@@ -18433,7 +18443,7 @@
         <v>76</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>83</v>
@@ -18448,15 +18458,15 @@
         <v>76</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18479,13 +18489,13 @@
         <v>76</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -18512,11 +18522,11 @@
         <v>76</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>76</v>
@@ -18534,7 +18544,7 @@
         <v>76</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>77</v>
@@ -18546,18 +18556,18 @@
         <v>76</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18580,16 +18590,16 @@
         <v>76</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -18597,7 +18607,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>76</v>
@@ -18639,7 +18649,7 @@
         <v>76</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>83</v>
@@ -18654,15 +18664,15 @@
         <v>76</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18685,13 +18695,13 @@
         <v>76</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -18742,7 +18752,7 @@
         <v>76</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>77</v>
@@ -18754,18 +18764,18 @@
         <v>76</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18788,16 +18798,16 @@
         <v>76</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -18805,7 +18815,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>76</v>
@@ -18847,7 +18857,7 @@
         <v>76</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>83</v>
@@ -18862,15 +18872,15 @@
         <v>76</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18893,13 +18903,13 @@
         <v>76</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -18950,7 +18960,7 @@
         <v>76</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>77</v>
@@ -18962,18 +18972,18 @@
         <v>76</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18996,16 +19006,16 @@
         <v>76</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -19013,7 +19023,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>76</v>
@@ -19055,7 +19065,7 @@
         <v>76</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>83</v>
@@ -19070,15 +19080,15 @@
         <v>76</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19101,13 +19111,13 @@
         <v>76</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -19158,7 +19168,7 @@
         <v>76</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>77</v>
@@ -19170,18 +19180,18 @@
         <v>76</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19204,16 +19214,16 @@
         <v>76</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -19221,7 +19231,7 @@
       </c>
       <c r="Q171" s="2"/>
       <c r="R171" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S171" t="s" s="2">
         <v>76</v>
@@ -19263,7 +19273,7 @@
         <v>76</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>83</v>
@@ -19278,15 +19288,15 @@
         <v>76</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19309,13 +19319,13 @@
         <v>76</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19366,7 +19376,7 @@
         <v>76</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>77</v>
@@ -19378,18 +19388,18 @@
         <v>76</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19412,16 +19422,16 @@
         <v>76</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -19471,7 +19481,7 @@
         <v>76</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>83</v>
@@ -19486,15 +19496,15 @@
         <v>76</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19517,13 +19527,13 @@
         <v>76</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19574,7 +19584,7 @@
         <v>76</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>77</v>
@@ -19586,18 +19596,18 @@
         <v>76</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19620,16 +19630,16 @@
         <v>76</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -19679,7 +19689,7 @@
         <v>76</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>83</v>
@@ -19694,15 +19704,15 @@
         <v>76</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19725,13 +19735,13 @@
         <v>76</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -19782,7 +19792,7 @@
         <v>76</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>77</v>
@@ -19794,10 +19804,10 @@
         <v>76</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:54:25+00:00</t>
+    <t>2026-06-24T09:36:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:36:36+00:00</t>
+    <t>2026-06-24T12:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:11:25+00:00</t>
+    <t>2026-06-24T12:16:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:27:57+00:00</t>
+    <t>2026-06-25T09:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.code='9999') implies ((extension.where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(where(url='motivation').valueCodeableConcept.coding.code='9999') implies ((where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
   </si>
   <si>
     <t>Extension.extension:typeDecision</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:12:27+00:00</t>
+    <t>2026-06-25T09:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(where(url='motivation').valueCodeableConcept.coding.code='9999') implies ((where(url='motivationLocale').valueString.exists()))}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists() implies extension.where(url='motivationLocale').valueString.exists()}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
   </si>
   <si>
     <t>Extension.extension:typeDecision</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:43:13+00:00</t>
+    <t>2026-06-25T10:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -261,7 +261,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').valueString.exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5'.exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
   </si>
   <si>
     <t>Extension.id</t>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists() implies extension.where(url='motivationLocale').valueString.exists()}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5') implies ((extension.where(url='dateEffetCloture').exists()))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Extension.extension:typeDecision</t>
@@ -2044,7 +2044,7 @@
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2250,7 +2250,7 @@
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
@@ -2561,7 +2561,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2767,7 +2767,7 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -3080,7 +3080,7 @@
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>76</v>
@@ -3286,7 +3286,7 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>76</v>
@@ -3599,7 +3599,7 @@
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>76</v>
@@ -3805,7 +3805,7 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -4116,7 +4116,7 @@
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>76</v>
@@ -4322,7 +4322,7 @@
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>76</v>
@@ -4635,7 +4635,7 @@
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
@@ -4841,7 +4841,7 @@
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>76</v>
@@ -5360,7 +5360,7 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>76</v>
@@ -5465,7 +5465,7 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>76</v>
@@ -5671,7 +5671,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -5982,7 +5982,7 @@
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
@@ -6188,7 +6188,7 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
@@ -6499,7 +6499,7 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
@@ -6705,7 +6705,7 @@
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
@@ -7016,7 +7016,7 @@
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
@@ -7222,7 +7222,7 @@
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>76</v>
@@ -7535,7 +7535,7 @@
         <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>76</v>
@@ -7741,7 +7741,7 @@
         <v>76</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>76</v>
@@ -8054,7 +8054,7 @@
         <v>76</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>76</v>
@@ -8260,7 +8260,7 @@
         <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>76</v>
@@ -8573,7 +8573,7 @@
         <v>76</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>76</v>
@@ -8779,7 +8779,7 @@
         <v>76</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>76</v>
@@ -9090,7 +9090,7 @@
         <v>76</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>76</v>
@@ -9296,7 +9296,7 @@
         <v>76</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>76</v>
@@ -9609,7 +9609,7 @@
         <v>76</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>76</v>
@@ -9815,7 +9815,7 @@
         <v>76</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>76</v>
@@ -10128,7 +10128,7 @@
         <v>76</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>76</v>
@@ -10334,7 +10334,7 @@
         <v>76</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>76</v>
@@ -10645,7 +10645,7 @@
         <v>76</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>76</v>
@@ -10851,7 +10851,7 @@
         <v>76</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>76</v>
@@ -11164,7 +11164,7 @@
         <v>76</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>76</v>
@@ -11370,7 +11370,7 @@
         <v>76</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>76</v>
@@ -11475,7 +11475,7 @@
         <v>76</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>76</v>
@@ -11681,7 +11681,7 @@
         <v>76</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>76</v>
@@ -11992,7 +11992,7 @@
         <v>76</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>76</v>
@@ -12198,7 +12198,7 @@
         <v>76</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>76</v>
@@ -12509,7 +12509,7 @@
         <v>76</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>76</v>
@@ -12715,7 +12715,7 @@
         <v>76</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>76</v>
@@ -13028,7 +13028,7 @@
         <v>76</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>76</v>
@@ -13234,7 +13234,7 @@
         <v>76</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>76</v>
@@ -13547,7 +13547,7 @@
         <v>76</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>76</v>
@@ -13753,7 +13753,7 @@
         <v>76</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>76</v>
@@ -14066,7 +14066,7 @@
         <v>76</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>76</v>
@@ -14272,7 +14272,7 @@
         <v>76</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>76</v>
@@ -14585,7 +14585,7 @@
         <v>76</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>76</v>
@@ -14791,7 +14791,7 @@
         <v>76</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>76</v>
@@ -15102,7 +15102,7 @@
         <v>76</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>76</v>
@@ -15308,7 +15308,7 @@
         <v>76</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>76</v>
@@ -15621,7 +15621,7 @@
         <v>76</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>76</v>
@@ -15829,7 +15829,7 @@
         <v>76</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>88</v>
@@ -15934,7 +15934,7 @@
         <v>76</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>76</v>
@@ -16140,7 +16140,7 @@
         <v>76</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>76</v>
@@ -16451,7 +16451,7 @@
         <v>76</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>76</v>
@@ -16659,7 +16659,7 @@
         <v>76</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>88</v>
@@ -16764,7 +16764,7 @@
         <v>76</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>76</v>
@@ -16970,7 +16970,7 @@
         <v>76</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>76</v>
@@ -17283,7 +17283,7 @@
         <v>76</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>76</v>
@@ -17489,7 +17489,7 @@
         <v>76</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>76</v>
@@ -17802,7 +17802,7 @@
         <v>76</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>76</v>
@@ -18008,7 +18008,7 @@
         <v>76</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>76</v>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:03:25+00:00</t>
+    <t>2026-06-25T10:20:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:20:08+00:00</t>
+    <t>2026-06-25T14:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -261,7 +261,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').valueString.exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.code='5'.exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').valueString.exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.where(code='5').exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
   </si>
   <si>
     <t>Extension.id</t>
@@ -507,8 +507,8 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation').exists())}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
- '6' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').exists().not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil').exists())}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton').exists())}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation'))}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
+ '6' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton'))}</t>
   </si>
   <si>
     <t>Extension.extension:droitPrestation.id</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-decision.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:41:02+00:00</t>
+    <t>2026-06-30T07:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
